--- a/tools/_out/brennancad_20261021/regen/stage/tee/DesignTable_6502_SW2.xlsx
+++ b/tools/_out/brennancad_20261021/regen/stage/tee/DesignTable_6502_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BU13"/>
+  <dimension ref="A1:BU14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2704,68 +2704,68 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6502-16-16-FG</t>
+          <t>6502-16-12-FG</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="C10" t="n">
         <v>0.65625</v>
       </c>
       <c r="D10" t="n">
-        <v>1.175</v>
+        <v>1.089</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5485</v>
+        <v>0.417</v>
       </c>
       <c r="F10" t="n">
-        <v>1.139</v>
+        <v>1.047</v>
       </c>
       <c r="G10" t="n">
-        <v>0.727</v>
+        <v>0.5928</v>
       </c>
       <c r="H10" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.749</v>
+        <v>0.6237</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6564</v>
+        <v>0.5998</v>
       </c>
       <c r="K10" t="n">
-        <v>0.86603</v>
+        <v>0.7216900000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="M10" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4873</v>
+        <v>0.4472</v>
       </c>
       <c r="O10" t="n">
-        <v>0.665</v>
+        <v>0.549</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9544</v>
+        <v>0.8623</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.604</v>
+        <v>0.481</v>
       </c>
       <c r="R10" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5475</v>
+        <v>0.4225</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6564</v>
+        <v>0.5998</v>
       </c>
       <c r="V10" t="n">
         <v>1.47</v>
@@ -2798,34 +2798,34 @@
         <v>37</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.84</v>
+        <v>0.609</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.84</v>
+        <v>0.844</v>
       </c>
       <c r="AI10" t="n">
         <v>1.47</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22228</v>
+        <v>0.97228</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.5252</v>
+        <v>0.4851</v>
       </c>
       <c r="AL10" t="n">
         <v>0.08333</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.61114</v>
+        <v>0.48614</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AP10" t="n">
         <v>1.3125</v>
@@ -2849,7 +2849,7 @@
         <v>1.3125</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.575</v>
+        <v>0.611</v>
       </c>
       <c r="AX10" t="n">
         <v>1.3125</v>
@@ -2873,37 +2873,37 @@
         <v>0.75727</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.575</v>
+        <v>0.611</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.036</v>
+        <v>0.042</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.48425</v>
+        <v>0.36075</v>
       </c>
       <c r="BH10" t="n">
         <v>1.13666</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.575</v>
+        <v>0.611</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.036</v>
+        <v>0.042</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.48425</v>
+        <v>0.36075</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.5485</v>
+        <v>0.417</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>6502-16-16-FG</t>
+          <t>6502-16-12-FG</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>45 deg Male JIC x Female Swivel Elbow, 1 5/16-12 (female 37deg JIC swivel) x 1 5/16-12 JIC</t>
+          <t>45 deg Male JIC x Female Swivel Elbow, 1 1/16-12 (female 37deg JIC swivel) x 1 5/16-12 JIC</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>1 5/16-12 (female 37deg JIC swivel)</t>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -2928,109 +2928,109 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>Air-Way s156 only (double-pass 22 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; swivel neck turned clear of the forged corner (Brennan 6502-12-12-FG STEP, tools/measure/neck45.py, 2026-10-01: body face 0.412, neck 0.417, nothing outside the neck from the body face to the nut rear face 0.453, where an untrimmed corner would stand 0.038 out; Brennan 1503-08-08-FG consistent): from the swivel body face to the swivel nut rear face the 30deg corner puck and the start corner of the angled hex arm are cut down to the neck radius (NECKTRIM1 revolve cut + NECKFILL1 ring back to the neck, in every configuration; no change where the corner stays inside the neck) - measured on ONE size whose corner stands out of the neck (-12), ASSUMED for the other sizes (-05); each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-CAD 2026-10-21: D1@BORE, D2@BORE, M2@DRIVE, M6@DRIVE, THDMAJ_B1@DRIVE, THDMAJ_B2@DRIVE, Y@HEX, M14@DRIVE, C3HEX@HEX] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; swivel neck turned clear of the forged corner (Brennan 6502-12-12-FG STEP, tools/measure/neck45.py, 2026-10-01: body face 0.412, neck 0.417, nothing outside the neck from the body face to the nut rear face 0.453, where an untrimmed corner would stand 0.038 out; Brennan 1503-08-08-FG consistent): from the swivel body face to the swivel nut rear face the 30deg corner puck and the start corner of the angled hex arm are cut down to the neck radius (NECKTRIM1 revolve cut + NECKFILL1 ring back to the neck, in every configuration; no change where the corner stays inside the neck) - measured on ONE size whose corner stands out of the neck (-12), ASSUMED for the other sizes (-05); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p035-t02: agrees on M2@DRIVE, M6@DRIVE, C3HEX@HEX, Y@HEX, D1@BORE, D2@BORE | DataStatus VERIFIED -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule); leg 1: the corner puck (radius 0.758) reaches 0.183 past the swivel body face (0.575) but stays inside the neck (max 0.494 off the axis vs neck radius 0.548) - as on the Brennan 6502-08-08-FG / 1503-08-08-FG forgings</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | Brennan CAD record 6502-16-12-FG (PARTcommunity / CADENAS, D1@BORE=B1D, D2@BORE=B2D, M2@DRIVE=M2, M6@DRIVE=M6, THDMAJ_B1@DRIVE=B1THD, THDMAJ_B2@DRIVE=B2THD, Y@HEX=Y, M14@DRIVE=M, C3HEX@HEX=C; user 2026-10-21 "yes you can use them following my rule") | hex A/F raised from Air-Way 1.312 to 1.3125 (JIC thread major; 2603HX rule); leg 1: the corner (puck radius 0.758) stands 0.031 out of the neck past the swivel body face (0.611; 0.448 off the axis vs neck radius 0.417) - turned down to the neck from the body face to the nut rear face (0.653) by NECKTRIM1 / NECKFILL1, as on the Brennan 6502-12-12-FG STEP (NECK-6502, 2026-10-01)</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>6502-16-16-FG</t>
+          <t>6502-16-12-FG</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6502-20-20-FG</t>
+          <t>6502-16-16-FG</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="D11" t="n">
-        <v>1.26</v>
+        <v>1.175</v>
       </c>
       <c r="E11" t="n">
-        <v>0.68</v>
+        <v>0.5485</v>
       </c>
       <c r="F11" t="n">
-        <v>1.145</v>
+        <v>1.139</v>
       </c>
       <c r="G11" t="n">
-        <v>0.949</v>
+        <v>0.727</v>
       </c>
       <c r="H11" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9889</v>
+        <v>0.749</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5375</v>
+        <v>0.6564</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1547</v>
+        <v>0.86603</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="M11" t="n">
-        <v>0.76739</v>
+        <v>0.61114</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4345</v>
+        <v>0.4873</v>
       </c>
       <c r="O11" t="n">
-        <v>0.88</v>
+        <v>0.665</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9556</v>
+        <v>0.9544</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.766</v>
+        <v>0.604</v>
       </c>
       <c r="R11" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7025</v>
+        <v>0.5475</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5375</v>
+        <v>0.6564</v>
       </c>
       <c r="V11" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="X11" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="Y11" t="n">
         <v>0.125</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="AD11" t="n">
         <v>60</v>
@@ -3039,43 +3039,43 @@
         <v>37</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.53478</v>
+        <v>1.22228</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.4724</v>
+        <v>0.5252</v>
       </c>
       <c r="AL11" t="n">
         <v>0.08333</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.76739</v>
+        <v>0.61114</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="AO11" t="n">
-        <v>2.03</v>
+        <v>1.75</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="AQ11" t="n">
         <v>0.08333</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="AS11" t="n">
         <v>0.04511</v>
@@ -3087,64 +3087,64 @@
         <v>0.08333</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.63</v>
+        <v>1.3125</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.77</v>
+        <v>0.575</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.63</v>
+        <v>1.3125</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.632</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.65625</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.47004</v>
+        <v>0.37839</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.47004</v>
+        <v>0.37839</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.94058</v>
+        <v>0.75727</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.77</v>
+        <v>0.575</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.115</v>
+        <v>0.036</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.61</v>
+        <v>0.48425</v>
       </c>
       <c r="BH11" t="n">
-        <v>1.41162</v>
+        <v>1.13666</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.77</v>
+        <v>0.575</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.115</v>
+        <v>0.036</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.61</v>
+        <v>0.48425</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.68</v>
+        <v>0.5485</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>6502-20-20-FG</t>
+          <t>6502-16-16-FG</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>45 deg Male JIC x Female Swivel Elbow, 1 5/8-12 (female 37deg JIC swivel) x 1 5/8-12 JIC</t>
+          <t>45 deg Male JIC x Female Swivel Elbow, 1 5/16-12 (female 37deg JIC swivel) x 1 5/16-12 JIC</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>1 5/8-12 (female 37deg JIC swivel)</t>
+          <t>1 5/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>1 5/8-12 JIC</t>
+          <t>1 5/16-12 JIC</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -3169,109 +3169,109 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>Air-Way s156 only (double-pass 22 rows); M14@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1972 = 1.410 (table had 1.4) [user 2026-10-18 A19]; M14@DRIVE: Air-Way 1.4 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.41) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; swivel neck turned clear of the forged corner (Brennan 6502-12-12-FG STEP, tools/measure/neck45.py, 2026-10-01: body face 0.412, neck 0.417, nothing outside the neck from the body face to the nut rear face 0.453, where an untrimmed corner would stand 0.038 out; Brennan 1503-08-08-FG consistent): from the swivel body face to the swivel nut rear face the 30deg corner puck and the start corner of the angled hex arm are cut down to the neck radius (NECKTRIM1 revolve cut + NECKFILL1 ring back to the neck, in every configuration; no change where the corner stays inside the neck) - measured on ONE size whose corner stands out of the neck (-12), ASSUMED for the other sizes (-05); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s156 only (double-pass 22 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; swivel neck turned clear of the forged corner (Brennan 6502-12-12-FG STEP, tools/measure/neck45.py, 2026-10-01: body face 0.412, neck 0.417, nothing outside the neck from the body face to the nut rear face 0.453, where an untrimmed corner would stand 0.038 out; Brennan 1503-08-08-FG consistent): from the swivel body face to the swivel nut rear face the 30deg corner puck and the start corner of the angled hex arm are cut down to the neck radius (NECKTRIM1 revolve cut + NECKFILL1 ring back to the neck, in every configuration; no change where the corner stays inside the neck) - measured on ONE size whose corner stands out of the neck (-12), ASSUMED for the other sizes (-05); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 2 settled): M14@DRIVE 1.4 -&gt; OMi 1.410 (Items!N1972, M134) | 2026-10-20 Air-Way first: M14@DRIVE OMi/Brennan 1.41 -&gt; Air-Way 1.4 | leg 1: the corner puck (radius 0.941) reaches 0.171 past the swivel body face (0.770) but stays inside the neck (max 0.541 off the axis vs neck radius 0.680) - as on the Brennan 6502-08-08-FG / 1503-08-08-FG forgings</t>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p035-t02: agrees on M2@DRIVE, M6@DRIVE, C3HEX@HEX, Y@HEX, D1@BORE, D2@BORE | DataStatus VERIFIED -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule); leg 1: the corner puck (radius 0.758) reaches 0.183 past the swivel body face (0.575) but stays inside the neck (max 0.494 off the axis vs neck radius 0.548) - as on the Brennan 6502-08-08-FG / 1503-08-08-FG forgings</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>6502-20-20-FG</t>
+          <t>6502-16-16-FG</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6502-24-24-FG</t>
+          <t>6502-20-20-FG</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>1.41</v>
+        <v>1.26</v>
       </c>
       <c r="E12" t="n">
-        <v>0.776</v>
+        <v>0.68</v>
       </c>
       <c r="F12" t="n">
-        <v>1.32</v>
+        <v>1.145</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0504</v>
+        <v>0.949</v>
       </c>
       <c r="H12" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1134</v>
+        <v>0.9889</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7063</v>
+        <v>0.5375</v>
       </c>
       <c r="K12" t="n">
-        <v>1.29904</v>
+        <v>1.1547</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="M12" t="n">
-        <v>0.89239</v>
+        <v>0.76739</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5295</v>
+        <v>0.4345</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>0.88</v>
       </c>
       <c r="P12" t="n">
-        <v>1.065</v>
+        <v>0.9556</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8885</v>
+        <v>0.766</v>
       </c>
       <c r="R12" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7025</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7063</v>
+        <v>0.5375</v>
       </c>
       <c r="V12" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="W12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="Y12" t="n">
         <v>0.125</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.5454</v>
+        <v>0.4316</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.1298</v>
+        <v>0.1288</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.2482</v>
+        <v>0.2382</v>
       </c>
       <c r="AD12" t="n">
         <v>60</v>
@@ -3280,43 +3280,43 @@
         <v>37</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.78478</v>
+        <v>1.53478</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.5674</v>
+        <v>0.4724</v>
       </c>
       <c r="AL12" t="n">
         <v>0.08333</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.89239</v>
+        <v>0.76739</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="AO12" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.08333</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.5454</v>
+        <v>0.4316</v>
       </c>
       <c r="AS12" t="n">
         <v>0.04511</v>
@@ -3328,64 +3328,64 @@
         <v>0.08333</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.697</v>
+        <v>0.632</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.54221</v>
+        <v>0.47004</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.54221</v>
+        <v>0.47004</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.08492</v>
+        <v>0.94058</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.09</v>
+        <v>0.115</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.7155</v>
+        <v>0.61</v>
       </c>
       <c r="BH12" t="n">
-        <v>1.62813</v>
+        <v>1.41162</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.09</v>
+        <v>0.115</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.7155</v>
+        <v>0.61</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.776</v>
+        <v>0.68</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>6502-24-24-FG</t>
+          <t>6502-20-20-FG</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>45 deg Male JIC x Female Swivel Elbow, 1 7/8-12 (female 37deg JIC swivel) x 1 7/8-12 JIC</t>
+          <t>45 deg Male JIC x Female Swivel Elbow, 1 5/8-12 (female 37deg JIC swivel) x 1 5/8-12 JIC</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>1 7/8-12 (female 37deg JIC swivel)</t>
+          <t>1 5/8-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>1 7/8-12 JIC</t>
+          <t>1 5/8-12 JIC</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -3410,109 +3410,109 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>Air-Way s156 only (double-pass 22 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; swivel neck turned clear of the forged corner (Brennan 6502-12-12-FG STEP, tools/measure/neck45.py, 2026-10-01: body face 0.412, neck 0.417, nothing outside the neck from the body face to the nut rear face 0.453, where an untrimmed corner would stand 0.038 out; Brennan 1503-08-08-FG consistent): from the swivel body face to the swivel nut rear face the 30deg corner puck and the start corner of the angled hex arm are cut down to the neck radius (NECKTRIM1 revolve cut + NECKFILL1 ring back to the neck, in every configuration; no change where the corner stays inside the neck) - measured on ONE size whose corner stands out of the neck (-12), ASSUMED for the other sizes (-05); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way s156 only (double-pass 22 rows); M14@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1972 = 1.410 (table had 1.4) [user 2026-10-18 A19]; M14@DRIVE: Air-Way 1.4 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.41) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; swivel neck turned clear of the forged corner (Brennan 6502-12-12-FG STEP, tools/measure/neck45.py, 2026-10-01: body face 0.412, neck 0.417, nothing outside the neck from the body face to the nut rear face 0.453, where an untrimmed corner would stand 0.038 out; Brennan 1503-08-08-FG consistent): from the swivel body face to the swivel nut rear face the 30deg corner puck and the start corner of the angled hex arm are cut down to the neck radius (NECKTRIM1 revolve cut + NECKFILL1 ring back to the neck, in every configuration; no change where the corner stays inside the neck) - measured on ONE size whose corner stands out of the neck (-12), ASSUMED for the other sizes (-05); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M14@DRIVE=1.52~1.520; M6@DRIVE=2.25~2.250; M2@DRIVE=1.78~1.780; Y@HEX=1.88~1.875; C3HEX@HEX=2.25~2.250; D1@BORE=1.31~1.312; D2@BORE=1.31~1.312 | DataStatus VERIFIED -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | leg 1: the corner puck (radius 1.085) reaches 0.245 past the swivel body face (0.840) but stays inside the neck (max 0.687 off the axis vs neck radius 0.776) - as on the Brennan 6502-08-08-FG / 1503-08-08-FG forgings</t>
+          <t>A19 (user 2026-10-18, group 2 settled): M14@DRIVE 1.4 -&gt; OMi 1.410 (Items!N1972, M134) | 2026-10-20 Air-Way first: M14@DRIVE OMi/Brennan 1.41 -&gt; Air-Way 1.4 | leg 1: the corner puck (radius 0.941) reaches 0.171 past the swivel body face (0.770) but stays inside the neck (max 0.541 off the axis vs neck radius 0.680) - as on the Brennan 6502-08-08-FG / 1503-08-08-FG forgings</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>6502-24-24-FG</t>
+          <t>6502-20-20-FG</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6502-32-32-FG</t>
+          <t>6502-24-24-FG</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.91</v>
+        <v>2.25</v>
       </c>
       <c r="C13" t="n">
-        <v>1.25</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0785</v>
+        <v>0.776</v>
       </c>
       <c r="F13" t="n">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3936</v>
+        <v>1.0504</v>
       </c>
       <c r="H13" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4242</v>
+        <v>1.1134</v>
       </c>
       <c r="J13" t="n">
-        <v>0.862</v>
+        <v>0.7063</v>
       </c>
       <c r="K13" t="n">
-        <v>1.66277</v>
+        <v>1.29904</v>
       </c>
       <c r="L13" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="M13" t="n">
-        <v>1.20489</v>
+        <v>0.89239</v>
       </c>
       <c r="N13" t="n">
-        <v>0.702</v>
+        <v>0.5295</v>
       </c>
       <c r="O13" t="n">
-        <v>1.325</v>
+        <v>1.01</v>
       </c>
       <c r="P13" t="n">
-        <v>1.4202</v>
+        <v>1.065</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.198</v>
+        <v>0.8885</v>
       </c>
       <c r="R13" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.7063</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W13" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="S13" t="n">
-        <v>1.1175</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.862</v>
-      </c>
-      <c r="V13" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X13" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="Y13" t="n">
         <v>0.125</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.7124</v>
+        <v>0.5454</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.19</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.1292</v>
+        <v>0.1298</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.3318</v>
+        <v>0.2482</v>
       </c>
       <c r="AD13" t="n">
         <v>60</v>
@@ -3521,43 +3521,43 @@
         <v>37</v>
       </c>
       <c r="AF13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI13" t="n">
         <v>1.78</v>
       </c>
-      <c r="AG13" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>2.22</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>2.40978</v>
+        <v>1.78478</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.7399</v>
+        <v>0.5674</v>
       </c>
       <c r="AL13" t="n">
         <v>0.08333</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.20489</v>
+        <v>0.89239</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="AO13" t="n">
-        <v>2.91</v>
+        <v>2.25</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.5</v>
+        <v>1.875</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.08333</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.7124</v>
+        <v>0.5454</v>
       </c>
       <c r="AS13" t="n">
         <v>0.04511</v>
@@ -3569,97 +3569,338 @@
         <v>0.08333</v>
       </c>
       <c r="AV13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.54221</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.54221</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.08492</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.7155</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1.62813</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.7155</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>6502-24-24-FG</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>45 deg Male JIC x Female Swivel Elbow, 1 7/8-12 (female 37deg JIC swivel) x 1 7/8-12 JIC</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>6502</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>1 7/8-12 JIC</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>Air-Way s156 only (double-pass 22 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; swivel neck turned clear of the forged corner (Brennan 6502-12-12-FG STEP, tools/measure/neck45.py, 2026-10-01: body face 0.412, neck 0.417, nothing outside the neck from the body face to the nut rear face 0.453, where an untrimmed corner would stand 0.038 out; Brennan 1503-08-08-FG consistent): from the swivel body face to the swivel nut rear face the 30deg corner puck and the start corner of the angled hex arm are cut down to the neck radius (NECKTRIM1 revolve cut + NECKFILL1 ring back to the neck, in every configuration; no change where the corner stays inside the neck) - measured on ONE size whose corner stands out of the neck (-12), ASSUMED for the other sizes (-05); each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M14@DRIVE=1.52~1.520; M6@DRIVE=2.25~2.250; M2@DRIVE=1.78~1.780; Y@HEX=1.88~1.875; C3HEX@HEX=2.25~2.250; D1@BORE=1.31~1.312; D2@BORE=1.31~1.312 | DataStatus VERIFIED -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | leg 1: the corner puck (radius 1.085) reaches 0.245 past the swivel body face (0.840) but stays inside the neck (max 0.687 off the axis vs neck radius 0.776) - as on the Brennan 6502-08-08-FG / 1503-08-08-FG forgings</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
+          <t>6502-24-24-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>6502-32-32-FG</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.0785</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.3936</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.4242</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.66277</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.20489</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.4202</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.1175</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>37</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>2.40978</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.7399</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.20489</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AP14" t="n">
         <v>2.5</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AQ14" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW14" t="n">
         <v>1.24</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="AX14" t="n">
         <v>2.5</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="AY14" t="n">
         <v>0.887</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="AZ14" t="n">
         <v>1.25</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BA14" t="n">
         <v>1.25</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BB14" t="n">
         <v>0.72119</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BC14" t="n">
         <v>0.72119</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BD14" t="n">
         <v>1.44288</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BE14" t="n">
         <v>1.24</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BF14" t="n">
         <v>0.06</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BG14" t="n">
         <v>0.98425</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BH14" t="n">
         <v>2.16506</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BI14" t="n">
         <v>1.24</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BJ14" t="n">
         <v>0.06</v>
       </c>
-      <c r="BK13" t="n">
+      <c r="BK14" t="n">
         <v>0.98425</v>
       </c>
-      <c r="BL13" t="n">
+      <c r="BL14" t="n">
         <v>1.0785</v>
       </c>
-      <c r="BM13" t="inlineStr">
+      <c r="BM14" t="inlineStr">
         <is>
           <t>6502-32-32-FG</t>
         </is>
       </c>
-      <c r="BN13" t="inlineStr">
+      <c r="BN14" t="inlineStr">
         <is>
           <t>45 deg Male JIC x Female Swivel Elbow, 2 1/2-12 (female 37deg JIC swivel) x 2 1/2-12 JIC</t>
         </is>
       </c>
-      <c r="BO13" t="inlineStr">
+      <c r="BO14" t="inlineStr">
         <is>
           <t>6502</t>
         </is>
       </c>
-      <c r="BP13" t="inlineStr">
+      <c r="BP14" t="inlineStr">
         <is>
           <t>2 1/2-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="BQ13" t="inlineStr">
+      <c r="BQ14" t="inlineStr">
         <is>
           <t>2 1/2-12 JIC</t>
         </is>
       </c>
-      <c r="BR13" t="inlineStr">
+      <c r="BR14" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="BS13" t="inlineStr">
+      <c r="BS14" t="inlineStr">
         <is>
           <t>Air-Way s156 only (double-pass 22 rows) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = Air-Way C3 over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at Air-Way L minus the to-seat length (Brennan within 0.01), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; swivel leg length = Air-Way M5 (crossing to the nut face), nose tip at Air-Way M10; swivel neck turned clear of the forged corner (Brennan 6502-12-12-FG STEP, tools/measure/neck45.py, 2026-10-01: body face 0.412, neck 0.417, nothing outside the neck from the body face to the nut rear face 0.453, where an untrimmed corner would stand 0.038 out; Brennan 1503-08-08-FG consistent): from the swivel body face to the swivel nut rear face the 30deg corner puck and the start corner of the angled hex arm are cut down to the neck radius (NECKTRIM1 revolve cut + NECKFILL1 ring back to the neck, in every configuration; no change where the corner stays inside the neck) - measured on ONE size whose corner stands out of the neck (-12), ASSUMED for the other sizes (-05); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BT13" t="inlineStr">
+      <c r="BT14" t="inlineStr">
         <is>
           <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M14@DRIVE=1.97~1.970; M6@DRIVE=2.91~2.910; M2@DRIVE=2.22~2.220; Y@HEX=2.5~2.500; C3HEX@HEX=2.88~2.875; D1@BORE=1.78~1.781; D2@BORE=1.78~1.781 | DataStatus VERIFIED -&gt; ASSUMED: the swivel nut/nose geometry is single-source (Brennan STEPs) | leg 1: the corner puck (radius 1.443) reaches 0.203 past the swivel body face (1.240) but stays inside the neck (max 0.739 off the axis vs neck radius 1.079) - as on the Brennan 6502-08-08-FG / 1503-08-08-FG forgings</t>
         </is>
       </c>
-      <c r="BU13" t="inlineStr">
+      <c r="BU14" t="inlineStr">
         <is>
           <t>6502-32-32-FG</t>
         </is>
